--- a/benchmark/data/opt_results.xlsx
+++ b/benchmark/data/opt_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFD40B8-990F-4155-A127-1DC0998A42CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E93BEC3-4DB8-4AD6-A55C-417E24A8D4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
   <si>
     <t>tool</t>
   </si>
@@ -166,10 +166,13 @@
     <t>ATGACCACCCTGGCTGGGGCCGTGCCACGGATGATGCGCCCAGGTCCCGGCCAGAATTATCCTAGAAGCGGCTTTCCCCTGGAGGTGTCCACACCACTGGGCCAGGGAAGGGTGAATCAGCTGGGCGGAGTGTTCATCAACGGCAGGCCCCTGCCAAACCACATTCGGCATAAGATCGTGGAGATGGCTCATCACGGCATCCGGCCCTGCGTGATCAGTAGGCAGCTGCGGGTGTCCCACGGCTGTGTGAGCAAGATTCTGTGTCGCTATCAGGAAACCGGATCCATCCGGCCTGGCGCCATTGGTGGCAGCAAGCCAAAGCAGGTGACCACACCCGACGTGGAGAAGAAGATCGAGGAGTATAAACGGGAGAACCCAGGCATGTTCAGCTGGGAGATTCGGGACAAACTGCTGAAAGACGCCGTGTGCGATAGGAACACCGTGCCCTCTGTGTCAAGTATCAGCAGAATTCTGAGGTCTAAGTTCGGAAAGGGCGAAGAGGAAGAGGCCGATCTGGAGAGAAAGGAGGCCGAGGAGAGCGAGAAGAAGGCTAAGCACTCTATCGACGGCATCCTGTCCGAACGGGCCTCCGCTCCCCAGTCTGATGAAGGATCTGACATCGACAGCGAGCCTGACCTGCCTCTGAAGCGAAAGCAGAGGAGAAGCCGCACCACCTTTACCGCCGAACAGCTGGAGGAGCTGGAGAGAGCCTTCGAGAGAACCCACTATCCTGATATCTACACTCGCGAGGAGCTGGCTCAGAGGGCCAAGCTGACCGAGGCTAGGGTGCAGGTGTGGTTCTCCAATCGGCGCGCCAGATGGAGGAAGCAAGCCGGCGCCAATCAGCTGATGGCCTTCAACCATCTGATCCCAGGCGGCTTCCCTCCAACCGCTATGCCAACCCTGCCTACCTACCAGCTGTCTGAGACCTCCTATCAGCCCACCAGCATCCCACAGGCCGTGAGTGACCCTTCCAGCACAGTGCACCGCCCCCAGCCCCTGCCTCCATCTACCGTGCACCAGTCCACCATTCCCTCCAATCCCGACAGTTCATCAGCATACTGCCTGCCATCAACCCGCCATGGATTCTCAAGCTACACCGACAGCTTTGTGCCACCCTCCGGCCCCTCCAATCCCATGAACCCAACAATCGGGAATGGACTGTCCCCTCAGGTGCCCTTCATCATTAGCTCCCAGATCAGTAGGAAATGA</t>
   </si>
   <si>
-    <t>BioRedis-engine</t>
-  </si>
-  <si>
     <t>https://github.com/jkubis96/BioRedis_engine</t>
+  </si>
+  <si>
+    <t>BIOREDIS-engine</t>
+  </si>
+  <si>
+    <t>https://github.com/jkubis96/BIOREDIS_engine</t>
   </si>
 </sst>
 </file>
@@ -700,10 +703,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -747,10 +750,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>

--- a/benchmark/data/opt_results.xlsx
+++ b/benchmark/data/opt_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E93BEC3-4DB8-4AD6-A55C-417E24A8D4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378F94AF-23C5-4436-80D1-D4CD922381FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>tool</t>
   </si>
@@ -166,13 +166,10 @@
     <t>ATGACCACCCTGGCTGGGGCCGTGCCACGGATGATGCGCCCAGGTCCCGGCCAGAATTATCCTAGAAGCGGCTTTCCCCTGGAGGTGTCCACACCACTGGGCCAGGGAAGGGTGAATCAGCTGGGCGGAGTGTTCATCAACGGCAGGCCCCTGCCAAACCACATTCGGCATAAGATCGTGGAGATGGCTCATCACGGCATCCGGCCCTGCGTGATCAGTAGGCAGCTGCGGGTGTCCCACGGCTGTGTGAGCAAGATTCTGTGTCGCTATCAGGAAACCGGATCCATCCGGCCTGGCGCCATTGGTGGCAGCAAGCCAAAGCAGGTGACCACACCCGACGTGGAGAAGAAGATCGAGGAGTATAAACGGGAGAACCCAGGCATGTTCAGCTGGGAGATTCGGGACAAACTGCTGAAAGACGCCGTGTGCGATAGGAACACCGTGCCCTCTGTGTCAAGTATCAGCAGAATTCTGAGGTCTAAGTTCGGAAAGGGCGAAGAGGAAGAGGCCGATCTGGAGAGAAAGGAGGCCGAGGAGAGCGAGAAGAAGGCTAAGCACTCTATCGACGGCATCCTGTCCGAACGGGCCTCCGCTCCCCAGTCTGATGAAGGATCTGACATCGACAGCGAGCCTGACCTGCCTCTGAAGCGAAAGCAGAGGAGAAGCCGCACCACCTTTACCGCCGAACAGCTGGAGGAGCTGGAGAGAGCCTTCGAGAGAACCCACTATCCTGATATCTACACTCGCGAGGAGCTGGCTCAGAGGGCCAAGCTGACCGAGGCTAGGGTGCAGGTGTGGTTCTCCAATCGGCGCGCCAGATGGAGGAAGCAAGCCGGCGCCAATCAGCTGATGGCCTTCAACCATCTGATCCCAGGCGGCTTCCCTCCAACCGCTATGCCAACCCTGCCTACCTACCAGCTGTCTGAGACCTCCTATCAGCCCACCAGCATCCCACAGGCCGTGAGTGACCCTTCCAGCACAGTGCACCGCCCCCAGCCCCTGCCTCCATCTACCGTGCACCAGTCCACCATTCCCTCCAATCCCGACAGTTCATCAGCATACTGCCTGCCATCAACCCGCCATGGATTCTCAAGCTACACCGACAGCTTTGTGCCACCCTCCGGCCCCTCCAATCCCATGAACCCAACAATCGGGAATGGACTGTCCCCTCAGGTGCCCTTCATCATTAGCTCCCAGATCAGTAGGAAATGA</t>
   </si>
   <si>
-    <t>https://github.com/jkubis96/BioRedis_engine</t>
-  </si>
-  <si>
-    <t>BIOREDIS-engine</t>
-  </si>
-  <si>
     <t>https://github.com/jkubis96/BIOREDIS_engine</t>
+  </si>
+  <si>
+    <t>BIOREDIS</t>
   </si>
 </sst>
 </file>
@@ -706,7 +703,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -753,7 +750,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
